--- a/data/satisfaction_detail/2026/1-6月/散客.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/散客.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>9.99</v>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>9.98</v>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.59</v>
+        <v>9.65</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>10</v>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.24</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.76</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.82</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>10</v>
@@ -553,7 +553,7 @@
         <v>9.65</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.76</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>10</v>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.82</v>
+        <v>9.85</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>10</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>10</v>
